--- a/data/紫竹/天福号紫竹餐厅_紫竹公园店_菜品库_20260427_0957_a645046d_1777255057541.xlsx
+++ b/data/紫竹/天福号紫竹餐厅_紫竹公园店_菜品库_20260427_0957_a645046d_1777255057541.xlsx
@@ -47,7 +47,7 @@
     <t>菜品状态</t>
   </si>
   <si>
-    <t>红烩牛腩焗意面（2-3人份）</t>
+    <t>浓汤番茄焗意面（2-3人份）</t>
   </si>
   <si>
     <t>主餐（意面、焗饭）</t>
@@ -56,63 +56,60 @@
     <t>普通菜</t>
   </si>
   <si>
+    <t>￥88.00</t>
+  </si>
+  <si>
+    <t>在售</t>
+  </si>
+  <si>
+    <t>意式肉酱焗意面（2-3人份）</t>
+  </si>
+  <si>
+    <t>奶油蘑菇意面</t>
+  </si>
+  <si>
+    <t>￥42.00</t>
+  </si>
+  <si>
+    <t>传统意式肉酱面</t>
+  </si>
+  <si>
+    <t>￥38.00</t>
+  </si>
+  <si>
+    <t>传统番茄海鲜意面（微辣）</t>
+  </si>
+  <si>
+    <t>￥48.00</t>
+  </si>
+  <si>
+    <t>海鲜炒乌冬面</t>
+  </si>
+  <si>
+    <t>甄选肉食混拼</t>
+  </si>
+  <si>
+    <t>主菜（肉类）</t>
+  </si>
+  <si>
+    <t>￥438.00</t>
+  </si>
+  <si>
+    <t>美式烟熏猪肋排</t>
+  </si>
+  <si>
+    <t>￥198.00</t>
+  </si>
+  <si>
+    <t>脆皮烤春鸡</t>
+  </si>
+  <si>
+    <t>黑松露香煎三文鱼</t>
+  </si>
+  <si>
     <t>￥98.00</t>
   </si>
   <si>
-    <t>在售</t>
-  </si>
-  <si>
-    <t>浓汤番茄焗意面（2-3人份）</t>
-  </si>
-  <si>
-    <t>￥88.00</t>
-  </si>
-  <si>
-    <t>意式肉酱焗意面（2-3人份）</t>
-  </si>
-  <si>
-    <t>奶油蘑菇意面</t>
-  </si>
-  <si>
-    <t>￥42.00</t>
-  </si>
-  <si>
-    <t>传统意式肉酱面</t>
-  </si>
-  <si>
-    <t>￥38.00</t>
-  </si>
-  <si>
-    <t>传统番茄海鲜意面（微辣）</t>
-  </si>
-  <si>
-    <t>￥48.00</t>
-  </si>
-  <si>
-    <t>海鲜炒乌冬面</t>
-  </si>
-  <si>
-    <t>甄选肉食混拼</t>
-  </si>
-  <si>
-    <t>主菜（肉类）</t>
-  </si>
-  <si>
-    <t>￥438.00</t>
-  </si>
-  <si>
-    <t>美式烟熏猪肋排</t>
-  </si>
-  <si>
-    <t>￥198.00</t>
-  </si>
-  <si>
-    <t>脆皮烤春鸡</t>
-  </si>
-  <si>
-    <t>黑松露香煎三文鱼</t>
-  </si>
-  <si>
     <t>澳洲谷饲M3带骨肉眼牛排</t>
   </si>
   <si>
@@ -587,9 +584,6 @@
     <t>草莓耶耶</t>
   </si>
   <si>
-    <t>青蔬鲜果饮（冷）</t>
-  </si>
-  <si>
     <t>日光鲜酿（冷）</t>
   </si>
   <si>
@@ -693,6 +687,12 @@
   </si>
   <si>
     <t>￥0.00</t>
+  </si>
+  <si>
+    <t>天福酱肘子焗饭</t>
+  </si>
+  <si>
+    <t>天福甄烤小香肠焗饭</t>
   </si>
 </sst>
 </file>
@@ -714,10 +714,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF222222"/>
-      <name val="Helvetica Neue"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1325,7 +1326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1656,7 +1657,7 @@
     <col min="4" max="5" width="11.0666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" spans="1:6">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="20.4" spans="1:6">
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1696,7 +1697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="20.4" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1710,18 +1711,18 @@
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="20.4" spans="1:6">
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -1730,13 +1731,13 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="20.4" spans="1:6">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1756,7 +1757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="20.4" spans="1:6">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1776,7 +1777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="20.4" spans="1:6">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1790,41 +1791,41 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" ht="20.4" spans="1:6">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="20.4" spans="1:6">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
@@ -1836,7 +1837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="20.4" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1844,39 +1845,39 @@
         <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" ht="20.4" spans="1:6">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="20.4" spans="1:6">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1884,59 +1885,59 @@
         <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="20.4" spans="1:6">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" ht="20.4" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" ht="20.4" spans="1:6">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1944,19 +1945,19 @@
         <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" ht="20.4" spans="1:6">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1964,19 +1965,19 @@
         <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" ht="20.4" spans="1:6">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1984,19 +1985,19 @@
         <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="20.4" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2004,19 +2005,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" ht="20.4" spans="1:6">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2024,59 +2025,59 @@
         <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" ht="20.4" spans="1:6">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" ht="20.4" spans="1:6">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" ht="20.4" spans="1:6">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2084,19 +2085,19 @@
         <v>43</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="20.4" spans="1:6">
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2104,39 +2105,39 @@
         <v>44</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" ht="20.4" spans="1:6">
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="25" ht="20.4" spans="1:6">
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2144,7 +2145,7 @@
         <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>8</v>
@@ -2156,27 +2157,27 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" ht="20.4" spans="1:6">
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="27" ht="20.4" spans="1:6">
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2184,99 +2185,99 @@
         <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" ht="20.4" spans="1:6">
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" ht="20.4" spans="1:6">
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" ht="20.4" spans="1:6">
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" ht="20.4" spans="1:6">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" ht="20.4" spans="1:6">
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2284,19 +2285,19 @@
         <v>61</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="F32" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="33" ht="20.4" spans="1:6">
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2304,39 +2305,39 @@
         <v>62</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="34" ht="20.4" spans="1:6">
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="35" ht="20.4" spans="1:6">
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2344,19 +2345,19 @@
         <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" ht="20.4" spans="1:6">
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2364,39 +2365,39 @@
         <v>67</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" ht="20.4" spans="1:6">
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="D37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="38" ht="20.4" spans="1:6">
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2404,19 +2405,19 @@
         <v>71</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="F38" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="39" ht="20.4" spans="1:6">
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2424,19 +2425,19 @@
         <v>72</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="40" ht="20.4" spans="1:6">
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2444,39 +2445,39 @@
         <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="41" ht="20.4" spans="1:6">
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="D41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="42" ht="20.4" spans="1:6">
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2484,7 +2485,7 @@
         <v>76</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>8</v>
@@ -2496,7 +2497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" ht="20.4" spans="1:6">
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2504,59 +2505,59 @@
         <v>77</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="44" ht="20.4" spans="1:6">
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="45" ht="20.4" spans="1:6">
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="46" ht="20.4" spans="1:6">
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -2564,19 +2565,19 @@
         <v>82</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="47" ht="20.4" spans="1:6">
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2584,19 +2585,19 @@
         <v>83</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="48" ht="20.4" spans="1:6">
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2604,39 +2605,39 @@
         <v>84</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="49" ht="20.4" spans="1:6">
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="D49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F49" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="50" ht="20.4" spans="1:6">
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2644,19 +2645,19 @@
         <v>88</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="51" ht="20.4" spans="1:6">
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2664,19 +2665,19 @@
         <v>89</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F51" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="52" ht="20.4" spans="1:6">
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2684,19 +2685,19 @@
         <v>90</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="F52" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="53" ht="20.4" spans="1:6">
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2704,59 +2705,59 @@
         <v>91</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="54" ht="20.4" spans="1:6">
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="D54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="55" ht="20.4" spans="1:6">
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F55" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="56" ht="20.4" spans="1:6">
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2764,19 +2765,19 @@
         <v>96</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="57" ht="20.4" spans="1:6">
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2784,19 +2785,19 @@
         <v>97</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="58" ht="20.4" spans="1:6">
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2804,39 +2805,39 @@
         <v>98</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59" ht="20.4" spans="1:6">
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="60" ht="20.4" spans="1:6">
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2844,19 +2845,19 @@
         <v>101</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="61" ht="20.4" spans="1:6">
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2864,19 +2865,19 @@
         <v>102</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="62" ht="20.4" spans="1:6">
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2884,19 +2885,19 @@
         <v>103</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="63" ht="20.4" spans="1:6">
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -2904,19 +2905,19 @@
         <v>104</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="64" ht="20.4" spans="1:6">
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -2924,19 +2925,19 @@
         <v>105</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="65" ht="20.4" spans="1:6">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2944,59 +2945,59 @@
         <v>106</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="66" ht="20.4" spans="1:6">
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="D66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>17</v>
+        <v>109</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="67" ht="20.4" spans="1:6">
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="68" ht="20.4" spans="1:6">
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3004,99 +3005,99 @@
         <v>111</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="69" ht="20.4" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="70" ht="20.4" spans="1:6">
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C70" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="71" ht="20.4" spans="1:6">
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="72" ht="20.4" spans="1:6">
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="73" ht="20.4" spans="1:6">
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -3104,19 +3105,19 @@
         <v>122</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="74" ht="20.4" spans="1:6">
+    <row r="74" spans="1:6">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3124,19 +3125,19 @@
         <v>123</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="75" ht="20.4" spans="1:6">
+    <row r="75" spans="1:6">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3144,19 +3145,19 @@
         <v>124</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="76" ht="20.4" spans="1:6">
+    <row r="76" spans="1:6">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3164,19 +3165,19 @@
         <v>125</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="77" ht="20.4" spans="1:6">
+    <row r="77" spans="1:6">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3184,19 +3185,19 @@
         <v>126</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="78" ht="20.4" spans="1:6">
+    <row r="78" spans="1:6">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3204,19 +3205,19 @@
         <v>127</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="79" ht="20.4" spans="1:6">
+    <row r="79" spans="1:6">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3224,19 +3225,19 @@
         <v>128</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="80" ht="20.4" spans="1:6">
+    <row r="80" spans="1:6">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3244,19 +3245,19 @@
         <v>129</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="81" ht="20.4" spans="1:6">
+    <row r="81" spans="1:6">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3264,39 +3265,39 @@
         <v>130</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="82" ht="20.4" spans="1:6">
+    <row r="82" spans="1:6">
       <c r="A82" s="1">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="83" ht="20.4" spans="1:6">
+    <row r="83" spans="1:6">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3304,39 +3305,39 @@
         <v>133</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="84" ht="20.4" spans="1:6">
+    <row r="84" spans="1:6">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="85" ht="20.4" spans="1:6">
+    <row r="85" spans="1:6">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3344,19 +3345,19 @@
         <v>136</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="86" ht="20.4" spans="1:6">
+    <row r="86" spans="1:6">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3364,19 +3365,19 @@
         <v>137</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="87" ht="20.4" spans="1:6">
+    <row r="87" spans="1:6">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3384,19 +3385,19 @@
         <v>138</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="88" ht="20.4" spans="1:6">
+    <row r="88" spans="1:6">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3404,59 +3405,59 @@
         <v>139</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="89" ht="20.4" spans="1:6">
+    <row r="89" spans="1:6">
       <c r="A89" s="1">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="90" ht="20.4" spans="1:6">
+    <row r="90" spans="1:6">
       <c r="A90" s="1">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="D90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="91" ht="20.4" spans="1:6">
+    <row r="91" spans="1:6">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3464,19 +3465,19 @@
         <v>144</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="92" ht="20.4" spans="1:6">
+    <row r="92" spans="1:6">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3484,19 +3485,19 @@
         <v>145</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="93" ht="20.4" spans="1:6">
+    <row r="93" spans="1:6">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3504,19 +3505,19 @@
         <v>146</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="94" ht="20.4" spans="1:6">
+    <row r="94" spans="1:6">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3524,19 +3525,19 @@
         <v>147</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="95" ht="20.4" spans="1:6">
+    <row r="95" spans="1:6">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -3544,19 +3545,19 @@
         <v>148</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="96" ht="20.4" spans="1:6">
+    <row r="96" spans="1:6">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -3564,19 +3565,19 @@
         <v>149</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="97" ht="20.4" spans="1:6">
+    <row r="97" spans="1:6">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -3584,19 +3585,19 @@
         <v>150</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="98" ht="20.4" spans="1:6">
+    <row r="98" spans="1:6">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -3604,19 +3605,19 @@
         <v>151</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="99" ht="20.4" spans="1:6">
+    <row r="99" spans="1:6">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -3624,59 +3625,59 @@
         <v>152</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="100" ht="20.4" spans="1:6">
+    <row r="100" spans="1:6">
       <c r="A100" s="1">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="101" ht="20.4" spans="1:6">
+    <row r="101" spans="1:6">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" ht="20.4" spans="1:6">
+    <row r="102" spans="1:6">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -3684,19 +3685,19 @@
         <v>157</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="103" ht="20.4" spans="1:6">
+    <row r="103" spans="1:6">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -3710,13 +3711,13 @@
         <v>8</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="104" ht="20.4" spans="1:6">
+    <row r="104" spans="1:6">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -3724,19 +3725,19 @@
         <v>159</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="105" ht="20.4" spans="1:6">
+    <row r="105" spans="1:6">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -3744,19 +3745,19 @@
         <v>160</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="106" ht="20.4" spans="1:6">
+    <row r="106" spans="1:6">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -3764,19 +3765,19 @@
         <v>161</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="107" ht="20.4" spans="1:6">
+    <row r="107" spans="1:6">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -3784,19 +3785,19 @@
         <v>162</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="108" ht="20.4" spans="1:6">
+    <row r="108" spans="1:6">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -3804,39 +3805,39 @@
         <v>163</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="109" ht="20.4" spans="1:6">
+    <row r="109" spans="1:6">
       <c r="A109" s="1">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="110" ht="20.4" spans="1:6">
+    <row r="110" spans="1:6">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -3844,19 +3845,19 @@
         <v>166</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="111" ht="20.4" spans="1:6">
+    <row r="111" spans="1:6">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -3864,59 +3865,59 @@
         <v>167</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="112" ht="20.4" spans="1:6">
+    <row r="112" spans="1:6">
       <c r="A112" s="1">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="D112" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="113" ht="20.4" spans="1:6">
+    <row r="113" spans="1:6">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>172</v>
+        <v>59</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="114" ht="20.4" spans="1:6">
+    <row r="114" spans="1:6">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -3924,19 +3925,19 @@
         <v>173</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="115" ht="20.4" spans="1:6">
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -3944,19 +3945,19 @@
         <v>174</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="116" ht="20.4" spans="1:6">
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -3964,19 +3965,19 @@
         <v>175</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="117" ht="20.4" spans="1:6">
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -3984,19 +3985,19 @@
         <v>176</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="118" ht="20.4" spans="1:6">
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -4004,19 +4005,19 @@
         <v>177</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="119" ht="20.4" spans="1:6">
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -4024,39 +4025,39 @@
         <v>178</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="120" ht="20.4" spans="1:6">
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="F120" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="121" ht="20.4" spans="1:6">
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -4064,19 +4065,19 @@
         <v>181</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="122" ht="20.4" spans="1:6">
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -4084,19 +4085,19 @@
         <v>182</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="123" ht="20.4" spans="1:6">
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -4104,19 +4105,19 @@
         <v>183</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="124" ht="20.4" spans="1:6">
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -4124,19 +4125,19 @@
         <v>184</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="F124" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="125" ht="20.4" spans="1:6">
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -4144,19 +4145,19 @@
         <v>185</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="126" ht="20.4" spans="1:6">
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -4164,19 +4165,19 @@
         <v>186</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="127" ht="20.4" spans="1:6">
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -4184,19 +4185,19 @@
         <v>187</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="128" ht="20.4" spans="1:6">
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -4204,19 +4205,19 @@
         <v>188</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="129" ht="20.4" spans="1:6">
+    <row r="129" spans="1:6">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -4224,79 +4225,79 @@
         <v>189</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="130" ht="20.4" spans="1:6">
+    <row r="130" spans="1:6">
       <c r="A130" s="1">
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="131" ht="20.4" spans="1:6">
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>192</v>
+        <v>64</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="132" ht="20.4" spans="1:6">
+    <row r="132" spans="1:6">
       <c r="A132" s="1">
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="133" ht="20.4" spans="1:6">
+    <row r="133" spans="1:6">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -4304,19 +4305,19 @@
         <v>195</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="134" ht="20.4" spans="1:6">
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -4324,19 +4325,19 @@
         <v>196</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="135" ht="20.4" spans="1:6">
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -4344,19 +4345,19 @@
         <v>197</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="136" ht="20.4" spans="1:6">
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -4364,19 +4365,19 @@
         <v>198</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="137" ht="20.4" spans="1:6">
+    <row r="137" spans="1:6">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -4384,19 +4385,19 @@
         <v>199</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="138" ht="20.4" spans="1:6">
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -4404,19 +4405,19 @@
         <v>200</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>194</v>
+        <v>74</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="139" ht="20.4" spans="1:6">
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -4424,19 +4425,19 @@
         <v>201</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="140" ht="20.4" spans="1:6">
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -4444,19 +4445,19 @@
         <v>202</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="141" ht="20.4" spans="1:6">
+    <row r="141" spans="1:6">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -4464,19 +4465,19 @@
         <v>203</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="142" ht="20.4" spans="1:6">
+    <row r="142" spans="1:6">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -4484,19 +4485,19 @@
         <v>204</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="143" ht="20.4" spans="1:6">
+    <row r="143" spans="1:6">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -4504,19 +4505,19 @@
         <v>205</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="144" ht="20.4" spans="1:6">
+    <row r="144" spans="1:6">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -4524,19 +4525,19 @@
         <v>206</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" ht="20.4" spans="1:6">
+    <row r="145" spans="1:6">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -4544,19 +4545,19 @@
         <v>207</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="146" ht="20.4" spans="1:6">
+    <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -4564,19 +4565,19 @@
         <v>208</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="147" ht="20.4" spans="1:6">
+    <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -4584,19 +4585,19 @@
         <v>209</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="148" ht="20.4" spans="1:6">
+    <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -4604,19 +4605,19 @@
         <v>210</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="149" ht="20.4" spans="1:6">
+    <row r="149" spans="1:6">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -4624,19 +4625,19 @@
         <v>211</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="150" ht="20.4" spans="1:6">
+    <row r="150" spans="1:6">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -4644,19 +4645,19 @@
         <v>212</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="151" ht="20.4" spans="1:6">
+    <row r="151" spans="1:6">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -4664,19 +4665,19 @@
         <v>213</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="152" ht="20.4" spans="1:6">
+    <row r="152" spans="1:6">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -4684,19 +4685,19 @@
         <v>214</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="153" ht="20.4" spans="1:6">
+    <row r="153" spans="1:6">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -4704,93 +4705,93 @@
         <v>215</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="154" ht="20.4" spans="1:6">
+    <row r="154" spans="1:6">
       <c r="A154" s="1">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>143</v>
+        <v>54</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="155" ht="20.4" spans="1:6">
+    <row r="155" spans="1:6">
       <c r="A155" s="1">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>143</v>
+        <v>168</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="156" ht="20.4" spans="1:6">
+    <row r="156" spans="1:6">
       <c r="A156" s="1">
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="157" ht="20.4" spans="1:6">
+    <row r="157" spans="1:6">
       <c r="A157" s="1">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>221</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>10</v>
